--- a/Predictive_Maintenance_dataset_22.xlsx.xlsx
+++ b/Predictive_Maintenance_dataset_22.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26bb60aab58ef9a7/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="842" documentId="11_2C44BDEC2040C98AC652E47DDCB6EBC61998AE3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A5BC2C2-15B5-4600-8D1A-700455CEF8B9}"/>
+  <xr:revisionPtr revIDLastSave="976" documentId="11_2C44BDEC2040C98AC652E47DDCB6EBC61998AE3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD6F6C89-FEA2-4F38-B0D1-36873CB0DE1B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="125">
   <si>
     <t xml:space="preserve">اسم الجهاز </t>
   </si>
@@ -621,6 +621,12 @@
       </rPr>
       <t>Last Update: May 2026</t>
     </r>
+  </si>
+  <si>
+    <t>Foaming</t>
+  </si>
+  <si>
+    <t>Ph</t>
   </si>
 </sst>
 </file>
@@ -715,7 +721,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -758,6 +764,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -797,7 +809,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -855,6 +867,18 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -864,25 +888,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3433,7 +3448,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41B326DE-5123-43CE-A193-4752D9F8D342}">
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -3520,7 +3535,7 @@
         <v>77</v>
       </c>
       <c r="I2" s="8">
-        <f>B2+C2+D2+E2</f>
+        <f t="shared" ref="I2:I11" si="0">B2+C2+D2+E2</f>
         <v>10</v>
       </c>
       <c r="J2" s="8" t="str">
@@ -3570,27 +3585,27 @@
         <v>79</v>
       </c>
       <c r="I3" s="8">
-        <f>B3+C3+D3+E3</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="J3" s="8" t="str">
-        <f t="shared" ref="J3:J6" si="0">IF(I3&gt;=8,"High",IF(I3&gt;=5,"Medium","Low"))</f>
+        <f t="shared" ref="J3:J6" si="1">IF(I3&gt;=8,"High",IF(I3&gt;=5,"Medium","Low"))</f>
         <v>High</v>
       </c>
       <c r="K3" s="8" t="str">
-        <f t="shared" ref="K3:K6" si="1">IF(TRIM(M3)="Critical","High-risk equipment: immediate action required",IF(TRIM(M3)="Warning","Moderate risk: inspection should be scheduled","Normal condition: continue routine monitoring"))</f>
+        <f t="shared" ref="K3:K6" si="2">IF(TRIM(M3)="Critical","High-risk equipment: immediate action required",IF(TRIM(M3)="Warning","Moderate risk: inspection should be scheduled","Normal condition: continue routine monitoring"))</f>
         <v>High-risk equipment: immediate action required</v>
       </c>
       <c r="L3" s="5" t="str">
-        <f t="shared" ref="L3:L6" si="2">IF(M3="Critical",IF(F3&gt;=2,"Predictive Maintenance","Continuous Monitoring"),IF(M3="Warning","Preventive Maintenance","Normal Operation"))</f>
+        <f t="shared" ref="L3:L6" si="3">IF(M3="Critical",IF(F3&gt;=2,"Predictive Maintenance","Continuous Monitoring"),IF(M3="Warning","Preventive Maintenance","Normal Operation"))</f>
         <v>Continuous Monitoring</v>
       </c>
       <c r="M3" s="9" t="str">
-        <f t="shared" ref="M3:M5" si="3">IF(I3&gt;=8,"Critical",IF(I3&gt;=5,"Warning","Normal"))</f>
+        <f t="shared" ref="M3:M5" si="4">IF(I3&gt;=8,"Critical",IF(I3&gt;=5,"Warning","Normal"))</f>
         <v>Critical</v>
       </c>
       <c r="N3" s="9" t="str">
-        <f t="shared" ref="N3:N7" si="4">IF(M3="Critical","Immediate Maintenance Required",IF(M3="Warning","Schedule Inspection","Continue Normal Operation"))</f>
+        <f t="shared" ref="N3:N7" si="5">IF(M3="Critical","Immediate Maintenance Required",IF(M3="Warning","Schedule Inspection","Continue Normal Operation"))</f>
         <v>Immediate Maintenance Required</v>
       </c>
     </row>
@@ -3620,27 +3635,27 @@
         <v>78</v>
       </c>
       <c r="I4" s="10">
-        <f>B4+C4+D4+E4</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="J4" s="8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Medium</v>
       </c>
       <c r="K4" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Moderate risk: inspection should be scheduled</v>
       </c>
       <c r="L4" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Preventive Maintenance</v>
       </c>
       <c r="M4" s="9" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Warning</v>
       </c>
       <c r="N4" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Schedule Inspection</v>
       </c>
     </row>
@@ -3670,27 +3685,27 @@
         <v>80</v>
       </c>
       <c r="I5" s="10">
-        <f>B5+C5+D5+E5</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="J5" s="8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Medium</v>
       </c>
       <c r="K5" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Moderate risk: inspection should be scheduled</v>
       </c>
       <c r="L5" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Preventive Maintenance</v>
       </c>
       <c r="M5" s="9" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Warning</v>
       </c>
       <c r="N5" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Schedule Inspection</v>
       </c>
     </row>
@@ -3720,19 +3735,19 @@
         <v>81</v>
       </c>
       <c r="I6" s="10">
-        <f>B6+C6+D6+E6</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="J6" s="8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Medium</v>
       </c>
       <c r="K6" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Moderate risk: inspection should be scheduled</v>
       </c>
       <c r="L6" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Preventive Maintenance</v>
       </c>
       <c r="M6" s="9" t="str">
@@ -3740,7 +3755,7 @@
         <v>Warning</v>
       </c>
       <c r="N6" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Schedule Inspection</v>
       </c>
     </row>
@@ -3770,27 +3785,27 @@
         <v>78</v>
       </c>
       <c r="I7" s="10">
-        <f>B7+C7+D7+E7</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="J7" s="8" t="str">
-        <f t="shared" ref="J7:J10" si="5">IF(I7&gt;=8,"High",IF(I7&gt;=5,"Medium","Low"))</f>
+        <f t="shared" ref="J7:J10" si="6">IF(I7&gt;=8,"High",IF(I7&gt;=5,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
       <c r="K7" s="8" t="str">
-        <f t="shared" ref="K7:K10" si="6">IF(TRIM(M7)="Critical","High-risk equipment: immediate action required",IF(TRIM(M7)="Warning","Moderate risk: inspection should be scheduled","Normal condition: continue routine monitoring"))</f>
+        <f t="shared" ref="K7:K10" si="7">IF(TRIM(M7)="Critical","High-risk equipment: immediate action required",IF(TRIM(M7)="Warning","Moderate risk: inspection should be scheduled","Normal condition: continue routine monitoring"))</f>
         <v>Moderate risk: inspection should be scheduled</v>
       </c>
       <c r="L7" s="5" t="str">
-        <f t="shared" ref="L7:L10" si="7">IF(M7="Critical",IF(F7&gt;=2,"Predictive Maintenance","Continuous Monitoring"),IF(M7="Warning","Preventive Maintenance","Normal Operation"))</f>
+        <f t="shared" ref="L7:L10" si="8">IF(M7="Critical",IF(F7&gt;=2,"Predictive Maintenance","Continuous Monitoring"),IF(M7="Warning","Preventive Maintenance","Normal Operation"))</f>
         <v>Preventive Maintenance</v>
       </c>
       <c r="M7" s="9" t="str">
-        <f t="shared" ref="M7:M9" si="8">IF(I7&gt;=8,"Critical",IF(I7&gt;=5,"Warning","Normal"))</f>
+        <f t="shared" ref="M7:M9" si="9">IF(I7&gt;=8,"Critical",IF(I7&gt;=5,"Warning","Normal"))</f>
         <v>Warning</v>
       </c>
       <c r="N7" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Schedule Inspection</v>
       </c>
     </row>
@@ -3820,26 +3835,26 @@
         <v>78</v>
       </c>
       <c r="I8" s="10">
-        <f>B8+C8+D8+E8</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="J8" s="8" t="str">
-        <f t="shared" ref="J8" si="9">IF(I8&gt;=8,"High",IF(I8&gt;=5,"Medium","Low"))</f>
+        <f t="shared" ref="J8" si="10">IF(I8&gt;=8,"High",IF(I8&gt;=5,"Medium","Low"))</f>
         <v>High</v>
       </c>
       <c r="K8" s="8" t="str">
-        <f t="shared" ref="K8" si="10">IF(TRIM(M8)="Critical","High-risk equipment: immediate action required",IF(TRIM(M8)="Warning","Moderate risk: inspection should be scheduled","Normal condition: continue routine monitoring"))</f>
+        <f t="shared" ref="K8" si="11">IF(TRIM(M8)="Critical","High-risk equipment: immediate action required",IF(TRIM(M8)="Warning","Moderate risk: inspection should be scheduled","Normal condition: continue routine monitoring"))</f>
         <v>High-risk equipment: immediate action required</v>
       </c>
       <c r="L8" s="5" t="str">
-        <f t="shared" ref="L8" si="11">IF(M8="Critical",IF(F8&gt;=2,"Predictive Maintenance","Continuous Monitoring"),IF(M8="Warning","Preventive Maintenance","Normal Operation"))</f>
+        <f t="shared" ref="L8" si="12">IF(M8="Critical",IF(F8&gt;=2,"Predictive Maintenance","Continuous Monitoring"),IF(M8="Warning","Preventive Maintenance","Normal Operation"))</f>
         <v>Predictive Maintenance</v>
       </c>
       <c r="M8" s="9" t="str">
-        <f t="shared" ref="M8" si="12">IF(I8&gt;=8,"Critical",IF(I8&gt;=5,"Warning","Normal"))</f>
+        <f t="shared" ref="M8" si="13">IF(I8&gt;=8,"Critical",IF(I8&gt;=5,"Warning","Normal"))</f>
         <v>Critical</v>
       </c>
-      <c r="N8" s="30"/>
+      <c r="N8" s="21"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
@@ -3867,23 +3882,23 @@
         <v>80</v>
       </c>
       <c r="I9" s="10">
-        <f>B9+C9+D9+E9</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="J9" s="8" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>High</v>
       </c>
       <c r="K9" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>High-risk equipment: immediate action required</v>
       </c>
       <c r="L9" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Predictive Maintenance</v>
       </c>
       <c r="M9" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Critical</v>
       </c>
     </row>
@@ -3913,19 +3928,19 @@
         <v>81</v>
       </c>
       <c r="I10" s="10">
-        <f>B10+C10+D10+E10</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="J10" s="8" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Medium</v>
       </c>
       <c r="K10" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Moderate risk: inspection should be scheduled</v>
       </c>
       <c r="L10" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Preventive Maintenance</v>
       </c>
       <c r="M10" s="9" t="str">
@@ -3959,159 +3974,204 @@
         <v>78</v>
       </c>
       <c r="I11" s="10">
-        <f>B11+C11+D11+E11</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="J11" s="8" t="str">
-        <f t="shared" ref="J11" si="13">IF(I11&gt;=8,"High",IF(I11&gt;=5,"Medium","Low"))</f>
+        <f t="shared" ref="J11:J23" si="14">IF(I11&gt;=8,"High",IF(I11&gt;=5,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
       <c r="K11" s="8" t="str">
-        <f t="shared" ref="K11" si="14">IF(TRIM(M11)="Critical","High-risk equipment: immediate action required",IF(TRIM(M11)="Warning","Moderate risk: inspection should be scheduled","Normal condition: continue routine monitoring"))</f>
+        <f t="shared" ref="K11:K23" si="15">IF(TRIM(M11)="Critical","High-risk equipment: immediate action required",IF(TRIM(M11)="Warning","Moderate risk: inspection should be scheduled","Normal condition: continue routine monitoring"))</f>
         <v>Moderate risk: inspection should be scheduled</v>
       </c>
       <c r="L11" s="5" t="str">
-        <f t="shared" ref="L11" si="15">IF(M11="Critical",IF(F11&gt;=2,"Predictive Maintenance","Continuous Monitoring"),IF(M11="Warning","Preventive Maintenance","Normal Operation"))</f>
+        <f t="shared" ref="L11:L23" si="16">IF(M11="Critical",IF(F11&gt;=2,"Predictive Maintenance","Continuous Monitoring"),IF(M11="Warning","Preventive Maintenance","Normal Operation"))</f>
         <v>Preventive Maintenance</v>
       </c>
       <c r="M11" s="9" t="str">
-        <f t="shared" ref="M11" si="16">IF(I11&gt;=8,"Critical",IF(I11&gt;=5,"Warning","Normal"))</f>
+        <f t="shared" ref="M11:M23" si="17">IF(I11&gt;=8,"Critical",IF(I11&gt;=5,"Warning","Normal"))</f>
         <v>Warning</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="9"/>
+      <c r="A12" s="5">
+        <v>4</v>
+      </c>
+      <c r="B12" s="5">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="I12" s="10">
+        <v>4</v>
+      </c>
+      <c r="J12" s="8" t="str">
+        <f t="shared" si="14"/>
+        <v>Low</v>
+      </c>
+      <c r="K12" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>Normal condition: continue routine monitoring</v>
+      </c>
+      <c r="L12" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>Normal Operation</v>
+      </c>
+      <c r="M12" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>Normal</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B13" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="5">
         <v>0</v>
       </c>
       <c r="D13" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="5">
         <v>0</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>88</v>
+        <v>123</v>
+      </c>
+      <c r="I13" s="10">
+        <v>8</v>
+      </c>
+      <c r="J13" s="8" t="str">
+        <f t="shared" si="14"/>
+        <v>High</v>
+      </c>
+      <c r="K13" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>High-risk equipment: immediate action required</v>
+      </c>
+      <c r="L13" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>Predictive Maintenance</v>
+      </c>
+      <c r="M13" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>Critical</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B14" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14" s="5">
         <v>0</v>
       </c>
       <c r="D14" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I14" s="11">
-        <v>0</v>
-      </c>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="N14" s="12" t="s">
-        <v>89</v>
+        <v>123</v>
+      </c>
+      <c r="I14" s="10">
+        <v>15</v>
+      </c>
+      <c r="J14" s="8" t="str">
+        <f t="shared" si="14"/>
+        <v>High</v>
+      </c>
+      <c r="K14" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>High-risk equipment: immediate action required</v>
+      </c>
+      <c r="L14" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>Predictive Maintenance</v>
+      </c>
+      <c r="M14" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>Critical</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B15" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E15" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F15" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I15" s="11">
-        <v>0</v>
-      </c>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="N15" s="12" t="s">
-        <v>89</v>
+        <v>123</v>
+      </c>
+      <c r="I15" s="10">
+        <v>21</v>
+      </c>
+      <c r="J15" s="8" t="str">
+        <f t="shared" si="14"/>
+        <v>High</v>
+      </c>
+      <c r="K15" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>High-risk equipment: immediate action required</v>
+      </c>
+      <c r="L15" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>Predictive Maintenance</v>
+      </c>
+      <c r="M15" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>Critical</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -4119,13 +4179,13 @@
         <v>0</v>
       </c>
       <c r="B16" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="5">
         <v>0</v>
       </c>
       <c r="D16" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="5">
         <v>0</v>
@@ -4137,182 +4197,677 @@
         <v>0</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="I16" s="11">
-        <v>0</v>
-      </c>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="M16" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="N16" s="12" t="s">
-        <v>89</v>
+        <v>79</v>
+      </c>
+      <c r="I16" s="10">
+        <v>3</v>
+      </c>
+      <c r="J16" s="8" t="str">
+        <f t="shared" si="14"/>
+        <v>Low</v>
+      </c>
+      <c r="K16" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>Normal condition: continue routine monitoring</v>
+      </c>
+      <c r="L16" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>Normal Operation</v>
+      </c>
+      <c r="M16" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>Normal</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B17" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="5">
         <v>0</v>
       </c>
       <c r="D17" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="5">
         <v>0</v>
       </c>
       <c r="H17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17" s="10">
+        <v>7</v>
+      </c>
+      <c r="J17" s="8" t="str">
+        <f t="shared" si="14"/>
+        <v>Medium</v>
+      </c>
+      <c r="K17" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>Moderate risk: inspection should be scheduled</v>
+      </c>
+      <c r="L17" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>Preventive Maintenance</v>
+      </c>
+      <c r="M17" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>Warning</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <v>4</v>
+      </c>
+      <c r="B18" s="5">
+        <v>2</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5">
+        <v>3</v>
+      </c>
+      <c r="E18" s="5">
+        <v>2</v>
+      </c>
+      <c r="F18" s="5">
+        <v>2</v>
+      </c>
+      <c r="G18" s="5">
+        <v>1</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18" s="10">
+        <v>14</v>
+      </c>
+      <c r="J18" s="8" t="str">
+        <f t="shared" si="14"/>
+        <v>High</v>
+      </c>
+      <c r="K18" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>High-risk equipment: immediate action required</v>
+      </c>
+      <c r="L18" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>Predictive Maintenance</v>
+      </c>
+      <c r="M18" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>Critical</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <v>6</v>
+      </c>
+      <c r="B19" s="5">
+        <v>3</v>
+      </c>
+      <c r="C19" s="5">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5">
+        <v>4</v>
+      </c>
+      <c r="E19" s="5">
+        <v>3</v>
+      </c>
+      <c r="F19" s="5">
+        <v>3</v>
+      </c>
+      <c r="G19" s="5">
+        <v>1</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" s="10">
+        <v>21</v>
+      </c>
+      <c r="J19" s="8" t="str">
+        <f t="shared" si="14"/>
+        <v>High</v>
+      </c>
+      <c r="K19" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>High-risk equipment: immediate action required</v>
+      </c>
+      <c r="L19" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>Predictive Maintenance</v>
+      </c>
+      <c r="M19" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>Critical</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <v>1</v>
+      </c>
+      <c r="B20" s="5">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5">
+        <v>0</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5">
+        <v>1</v>
+      </c>
+      <c r="G20" s="5">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I20" s="10">
+        <v>1</v>
+      </c>
+      <c r="J20" s="8" t="str">
+        <f t="shared" si="14"/>
+        <v>Low</v>
+      </c>
+      <c r="K20" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>Normal condition: continue routine monitoring</v>
+      </c>
+      <c r="L20" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>Normal Operation</v>
+      </c>
+      <c r="M20" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
+        <v>2</v>
+      </c>
+      <c r="B21" s="5">
+        <v>1</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5">
+        <v>1</v>
+      </c>
+      <c r="F21" s="5">
+        <v>1</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I21" s="10">
+        <v>6</v>
+      </c>
+      <c r="J21" s="8" t="str">
+        <f t="shared" si="14"/>
+        <v>Medium</v>
+      </c>
+      <c r="K21" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>Moderate risk: inspection should be scheduled</v>
+      </c>
+      <c r="L21" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>Preventive Maintenance</v>
+      </c>
+      <c r="M21" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>Warning</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
+        <v>4</v>
+      </c>
+      <c r="B22" s="5">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5">
+        <v>2</v>
+      </c>
+      <c r="E22" s="5">
+        <v>2</v>
+      </c>
+      <c r="F22" s="5">
+        <v>2</v>
+      </c>
+      <c r="G22" s="5">
+        <v>1</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I22" s="10">
+        <v>13</v>
+      </c>
+      <c r="J22" s="8" t="str">
+        <f t="shared" si="14"/>
+        <v>High</v>
+      </c>
+      <c r="K22" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>High-risk equipment: immediate action required</v>
+      </c>
+      <c r="L22" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>Predictive Maintenance</v>
+      </c>
+      <c r="M22" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>Critical</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
+        <v>5</v>
+      </c>
+      <c r="B23" s="5">
+        <v>3</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5">
+        <v>3</v>
+      </c>
+      <c r="E23" s="5">
+        <v>2</v>
+      </c>
+      <c r="F23" s="5">
+        <v>3</v>
+      </c>
+      <c r="G23" s="5">
+        <v>1</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I23" s="10">
+        <v>17</v>
+      </c>
+      <c r="J23" s="8" t="str">
+        <f t="shared" si="14"/>
+        <v>High</v>
+      </c>
+      <c r="K23" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>High-risk equipment: immediate action required</v>
+      </c>
+      <c r="L23" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>Predictive Maintenance</v>
+      </c>
+      <c r="M23" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>Critical</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
+        <v>0</v>
+      </c>
+      <c r="B25" s="5">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5">
+        <v>0</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
+        <v>0</v>
+      </c>
+      <c r="B26" s="5">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5">
+        <v>0</v>
+      </c>
+      <c r="D26" s="5">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5">
+        <v>1</v>
+      </c>
+      <c r="G26" s="5">
+        <v>0</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I26" s="11">
+        <v>0</v>
+      </c>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
+        <v>0</v>
+      </c>
+      <c r="B27" s="5">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5">
+        <v>0</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I27" s="11">
+        <v>0</v>
+      </c>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
+        <v>0</v>
+      </c>
+      <c r="B28" s="5">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5">
+        <v>0</v>
+      </c>
+      <c r="D28" s="5">
+        <v>0</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5">
+        <v>0</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I28" s="11">
+        <v>0</v>
+      </c>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="5">
+        <v>0</v>
+      </c>
+      <c r="B29" s="5">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5">
+        <v>0</v>
+      </c>
+      <c r="D29" s="5">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5">
+        <v>0</v>
+      </c>
+      <c r="H29" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="I17" s="11">
-        <v>0</v>
-      </c>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="5" t="s">
+      <c r="I29" s="11">
+        <v>0</v>
+      </c>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="M17" s="11" t="s">
+      <c r="M29" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="N17" s="12" t="s">
+      <c r="N29" s="12" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="27" t="s">
+    <row r="35" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="G23" s="24" t="s">
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="G35" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="28"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="28"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="28"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="24"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="28"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="24"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
-      <c r="M30" s="24"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" s="23"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="24"/>
+      <c r="K36" s="24"/>
+      <c r="L36" s="24"/>
+      <c r="M36" s="24"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="23"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="24"/>
+      <c r="K37" s="24"/>
+      <c r="L37" s="24"/>
+      <c r="M37" s="24"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" s="23"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="24"/>
+      <c r="K38" s="24"/>
+      <c r="L38" s="24"/>
+      <c r="M38" s="24"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="24"/>
+      <c r="J39" s="24"/>
+      <c r="K39" s="24"/>
+      <c r="L39" s="24"/>
+      <c r="M39" s="24"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="24"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="24"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="24"/>
+      <c r="M41" s="24"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="24"/>
+      <c r="K43" s="24"/>
+      <c r="L43" s="24"/>
+      <c r="M43" s="24"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I6">
     <sortCondition descending="1" ref="I1:I6"/>
   </sortState>
   <mergeCells count="2">
-    <mergeCell ref="A23:E27"/>
-    <mergeCell ref="G23:M31"/>
+    <mergeCell ref="A35:E39"/>
+    <mergeCell ref="G35:M43"/>
   </mergeCells>
-  <conditionalFormatting sqref="M2:M12">
+  <conditionalFormatting sqref="M2:M24">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="Normal">
       <formula>NOT(ISERROR(SEARCH("Normal",M2)))</formula>
     </cfRule>
@@ -4348,23 +4903,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -4541,63 +5096,63 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
+      <c r="A22" s="26"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
+      <c r="A23" s="26"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
+      <c r="A29" s="26"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
     </row>
     <row r="32" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="27" t="s">
         <v>121</v>
       </c>
       <c r="B32" s="24"/>
@@ -4859,10 +5414,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="29"/>
+      <c r="B1" s="30"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -4897,10 +5452,10 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="29"/>
+      <c r="B7" s="30"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -4927,10 +5482,10 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="29"/>
+      <c r="B12" s="30"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
@@ -4965,10 +5520,10 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="29"/>
+      <c r="B18" s="30"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
@@ -5019,10 +5574,10 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="29"/>
+      <c r="B26" s="30"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
